--- a/0_documents/2_docs/indiv_model_results_multiagent_20250529.xlsx
+++ b/0_documents/2_docs/indiv_model_results_multiagent_20250529.xlsx
@@ -8,15 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andrew/Documents/04_git/code-generation/0_documents/2_docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7D6F1D5-13BE-D446-ADEC-BF28C2172A78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EE15FE1-84F4-D547-9AFA-DEE6C0F64CAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="22360" windowHeight="17480" xr2:uid="{C9D0F527-0BC8-1244-93BD-714AFEC4ED61}"/>
+    <workbookView xWindow="0" yWindow="2940" windowWidth="23980" windowHeight="15140" activeTab="4" xr2:uid="{C9D0F527-0BC8-1244-93BD-714AFEC4ED61}"/>
   </bookViews>
   <sheets>
     <sheet name="HumanEval_Multiagent" sheetId="22" r:id="rId1"/>
     <sheet name="BigCode_Multiagent" sheetId="23" r:id="rId2"/>
     <sheet name="MBPP_Multiagent" sheetId="11" r:id="rId3"/>
     <sheet name="LBPP_Multiagent" sheetId="24" r:id="rId4"/>
+    <sheet name="Multiagent vs. Reflection" sheetId="25" r:id="rId5"/>
+    <sheet name="Sheet2" sheetId="26" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="40">
   <si>
     <t>#</t>
   </si>
@@ -115,11 +117,59 @@
   <si>
     <t>max</t>
   </si>
+  <si>
+    <t>Multiagent vs. Reflection Results (Pre-Normalization)</t>
+  </si>
+  <si>
+    <t>HumanEval</t>
+  </si>
+  <si>
+    <t>Bigcode</t>
+  </si>
+  <si>
+    <t>MBPP</t>
+  </si>
+  <si>
+    <t>LBPP</t>
+  </si>
+  <si>
+    <t>Dataset</t>
+  </si>
+  <si>
+    <t>Max. Reflection Result</t>
+  </si>
+  <si>
+    <t>Max. Multiagent Result</t>
+  </si>
+  <si>
+    <t>Gain</t>
+  </si>
+  <si>
+    <t>MEAN</t>
+  </si>
+  <si>
+    <t>Max. Single-Pass Results</t>
+  </si>
+  <si>
+    <t>Gain Multi vs. Reflect</t>
+  </si>
+  <si>
+    <t>Gain Reflect vs. Single-Pass</t>
+  </si>
+  <si>
+    <t>Gain Multi vs. Single-Pass</t>
+  </si>
+  <si>
+    <t>All vs. All Results (Pre-Normalization)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0000"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -136,7 +186,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -149,8 +199,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="13">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -294,11 +350,40 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -347,7 +432,35 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -684,7 +797,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{418CECD7-15F9-2A41-B7A3-02035A697F27}">
-  <dimension ref="A1:Q14"/>
+  <dimension ref="A1:R14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.1640625" bestFit="1" customWidth="1"/>
@@ -702,10 +815,10 @@
     <col min="14" max="14" width="7.1640625" customWidth="1"/>
     <col min="15" max="15" width="7.5" customWidth="1"/>
     <col min="16" max="16" width="7.33203125" customWidth="1"/>
-    <col min="17" max="17" width="7.83203125" customWidth="1"/>
+    <col min="17" max="18" width="7.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="158" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" ht="158" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -758,7 +871,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" s="9">
         <v>1</v>
       </c>
@@ -811,7 +924,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A3" s="10">
         <v>2</v>
       </c>
@@ -864,7 +977,7 @@
         <v>0.707213456554176</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A4" s="10">
         <v>3</v>
       </c>
@@ -917,7 +1030,7 @@
         <v>0.69481673844347303</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="11">
         <v>4</v>
       </c>
@@ -970,7 +1083,7 @@
         <v>0.69973126125519602</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A6" s="9">
         <v>5</v>
       </c>
@@ -1023,7 +1136,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A7" s="10">
         <v>6</v>
       </c>
@@ -1076,7 +1189,7 @@
         <v>0.64163676085858901</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A8" s="10">
         <v>7</v>
       </c>
@@ -1129,7 +1242,7 @@
         <v>0.65773740216802101</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11">
         <v>8</v>
       </c>
@@ -1182,7 +1295,7 @@
         <v>0.64838695143698999</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A10" s="9">
         <v>9</v>
       </c>
@@ -1235,7 +1348,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A11" s="10">
         <v>10</v>
       </c>
@@ -1288,7 +1401,7 @@
         <v>0.51042915756461105</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A12" s="10">
         <v>11</v>
       </c>
@@ -1341,7 +1454,7 @@
         <v>0.58318243314705198</v>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13" s="11">
         <v>12</v>
       </c>
@@ -1394,8 +1507,8 @@
         <v>0.58522846257572603</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B14" s="20" t="s">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="B14" s="17" t="s">
         <v>24</v>
       </c>
       <c r="G14">
@@ -1441,6 +1554,10 @@
       <c r="Q14">
         <f t="shared" si="0"/>
         <v>0.707213456554176</v>
+      </c>
+      <c r="R14">
+        <f>MAX(G14:Q14)</f>
+        <v>0.853794298207594</v>
       </c>
     </row>
   </sheetData>
@@ -1451,7 +1568,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6476CE9-6AC9-F74E-A626-22FBE9F82B51}">
-  <dimension ref="A1:Q14"/>
+  <dimension ref="A1:R14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.1640625" bestFit="1" customWidth="1"/>
@@ -1468,7 +1585,7 @@
     <col min="17" max="17" width="6.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="158" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" ht="158" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1521,7 +1638,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" s="9">
         <v>1</v>
       </c>
@@ -1574,7 +1691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A3" s="10">
         <v>2</v>
       </c>
@@ -1627,7 +1744,7 @@
         <v>0.31464905673079802</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A4" s="10">
         <v>3</v>
       </c>
@@ -1680,7 +1797,7 @@
         <v>0.32904102840562799</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="11">
         <v>4</v>
       </c>
@@ -1733,7 +1850,7 @@
         <v>0.31511864238604498</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A6" s="9">
         <v>5</v>
       </c>
@@ -1786,7 +1903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A7" s="10">
         <v>6</v>
       </c>
@@ -1839,7 +1956,7 @@
         <v>0.24618837444246799</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A8" s="10">
         <v>7</v>
       </c>
@@ -1892,7 +2009,7 @@
         <v>0.30337868018721398</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11">
         <v>8</v>
       </c>
@@ -1945,7 +2062,7 @@
         <v>0.24541114029628899</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A10" s="9">
         <v>9</v>
       </c>
@@ -1998,7 +2115,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A11" s="10">
         <v>10</v>
       </c>
@@ -2051,7 +2168,7 @@
         <v>0.167318658588335</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A12" s="10">
         <v>11</v>
       </c>
@@ -2104,7 +2221,7 @@
         <v>0.19115080391564501</v>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13" s="11">
         <v>12</v>
       </c>
@@ -2157,7 +2274,7 @@
         <v>0.18081465309310099</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="G14">
         <f>MAX(G2:G13)</f>
         <v>0.33080114536022798</v>
@@ -2201,6 +2318,10 @@
       <c r="Q14">
         <f t="shared" si="0"/>
         <v>0.32904102840562799</v>
+      </c>
+      <c r="R14">
+        <f>MAX(G14:Q14)</f>
+        <v>0.36366962680555998</v>
       </c>
     </row>
   </sheetData>
@@ -2211,7 +2332,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7177EE37-76A1-244B-B3C6-89EE825C6972}">
-  <dimension ref="A1:Q14"/>
+  <dimension ref="A1:R14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.1640625" bestFit="1" customWidth="1"/>
@@ -2223,7 +2344,7 @@
     <col min="7" max="17" width="6.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="158" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" ht="158" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -2276,7 +2397,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" s="9">
         <v>1</v>
       </c>
@@ -2329,7 +2450,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A3" s="10">
         <v>2</v>
       </c>
@@ -2382,7 +2503,7 @@
         <v>0.56319907659189195</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A4" s="10">
         <v>3</v>
       </c>
@@ -2435,7 +2556,7 @@
         <v>0.54867225740187298</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="11">
         <v>4</v>
       </c>
@@ -2488,7 +2609,7 @@
         <v>0.55064987043762004</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A6" s="9">
         <v>5</v>
       </c>
@@ -2541,7 +2662,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A7" s="10">
         <v>6</v>
       </c>
@@ -2594,7 +2715,7 @@
         <v>0.53603563329876802</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A8" s="10">
         <v>7</v>
       </c>
@@ -2647,7 +2768,7 @@
         <v>0.52927893762064904</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11">
         <v>8</v>
       </c>
@@ -2700,7 +2821,7 @@
         <v>0.519395476596617</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A10" s="9">
         <v>9</v>
       </c>
@@ -2753,7 +2874,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A11" s="10">
         <v>10</v>
       </c>
@@ -2806,7 +2927,7 @@
         <v>0.54279362378684803</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A12" s="10">
         <v>11</v>
       </c>
@@ -2859,7 +2980,7 @@
         <v>0.54624288313493397</v>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13" s="11">
         <v>12</v>
       </c>
@@ -2912,53 +3033,57 @@
         <v>0.55932373863299001</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B14" s="20" t="s">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="B14" s="17" t="s">
         <v>24</v>
       </c>
       <c r="G14">
-        <f t="shared" ref="G14" si="0">MAX(G2:G13)</f>
+        <f>MAX(G2:G13)</f>
         <v>0.51487062811102002</v>
       </c>
       <c r="H14">
-        <f t="shared" ref="H14" si="1">MAX(H2:H13)</f>
+        <f t="shared" ref="H14:Q14" si="0">MAX(H2:H13)</f>
         <v>0.64325352971674998</v>
       </c>
       <c r="I14">
-        <f t="shared" ref="I14" si="2">MAX(I2:I13)</f>
+        <f t="shared" si="0"/>
         <v>0.52753881373672995</v>
       </c>
       <c r="J14">
-        <f t="shared" ref="J14" si="3">MAX(J2:J13)</f>
+        <f t="shared" si="0"/>
         <v>0.67783973685261401</v>
       </c>
       <c r="K14">
-        <f t="shared" ref="K14" si="4">MAX(K2:K13)</f>
+        <f t="shared" si="0"/>
         <v>0.64649350992138799</v>
       </c>
       <c r="L14">
-        <f t="shared" ref="L14" si="5">MAX(L2:L13)</f>
+        <f t="shared" si="0"/>
         <v>0.66370382750555501</v>
       </c>
       <c r="M14">
-        <f t="shared" ref="M14" si="6">MAX(M2:M13)</f>
+        <f t="shared" si="0"/>
         <v>0.75792075706620698</v>
       </c>
       <c r="N14">
-        <f t="shared" ref="N14" si="7">MAX(N2:N13)</f>
+        <f t="shared" si="0"/>
         <v>0.75157276181722998</v>
       </c>
       <c r="O14">
-        <f t="shared" ref="O14" si="8">MAX(O2:O13)</f>
+        <f t="shared" si="0"/>
         <v>0.57436258253205097</v>
       </c>
       <c r="P14">
-        <f t="shared" ref="P14" si="9">MAX(P2:P13)</f>
+        <f t="shared" si="0"/>
         <v>0.62862256486569701</v>
       </c>
       <c r="Q14">
-        <f t="shared" ref="Q14" si="10">MAX(Q2:Q13)</f>
+        <f t="shared" si="0"/>
         <v>0.56319907659189195</v>
+      </c>
+      <c r="R14">
+        <f>MAX(G14:Q14)</f>
+        <v>0.75792075706620698</v>
       </c>
     </row>
   </sheetData>
@@ -2969,7 +3094,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{884B7DD8-E922-0A4E-97DF-0FECB7493F74}">
-  <dimension ref="A1:Q13"/>
+  <dimension ref="A1:R14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.1640625" bestFit="1" customWidth="1"/>
@@ -2981,7 +3106,7 @@
     <col min="7" max="17" width="6.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="158" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" ht="158" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -3034,7 +3159,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" s="9">
         <v>1</v>
       </c>
@@ -3087,7 +3212,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A3" s="10">
         <v>2</v>
       </c>
@@ -3140,7 +3265,7 @@
         <v>0.27960583034798597</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A4" s="10">
         <v>3</v>
       </c>
@@ -3193,7 +3318,7 @@
         <v>0.27638344209785798</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="11">
         <v>4</v>
       </c>
@@ -3246,7 +3371,7 @@
         <v>0.28825549023491398</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A6" s="9">
         <v>5</v>
       </c>
@@ -3299,7 +3424,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A7" s="10">
         <v>6</v>
       </c>
@@ -3352,7 +3477,7 @@
         <v>0.25174199090152599</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A8" s="10">
         <v>7</v>
       </c>
@@ -3405,7 +3530,7 @@
         <v>0.23270373765031799</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11">
         <v>8</v>
       </c>
@@ -3458,7 +3583,7 @@
         <v>0.264453574842691</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A10" s="9">
         <v>9</v>
       </c>
@@ -3511,7 +3636,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A11" s="10">
         <v>10</v>
       </c>
@@ -3564,7 +3689,7 @@
         <v>0.24060739068760301</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A12" s="10">
         <v>11</v>
       </c>
@@ -3617,7 +3742,7 @@
         <v>0.229503904977506</v>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13" s="11">
         <v>12</v>
       </c>
@@ -3668,10 +3793,461 @@
       </c>
       <c r="Q13">
         <v>0.245081407574717</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="G14">
+        <f>MAX(G2:G13)</f>
+        <v>0.232291517762681</v>
+      </c>
+      <c r="H14">
+        <f t="shared" ref="H14:Q14" si="0">MAX(H2:H13)</f>
+        <v>0.30139139905640999</v>
+      </c>
+      <c r="I14">
+        <f t="shared" si="0"/>
+        <v>0.22514383899854101</v>
+      </c>
+      <c r="J14">
+        <f t="shared" si="0"/>
+        <v>0.29325586412446197</v>
+      </c>
+      <c r="K14">
+        <f t="shared" si="0"/>
+        <v>0.33537643784593801</v>
+      </c>
+      <c r="L14">
+        <f t="shared" si="0"/>
+        <v>0.32163039046603997</v>
+      </c>
+      <c r="M14">
+        <f t="shared" si="0"/>
+        <v>0.30033746446649101</v>
+      </c>
+      <c r="N14">
+        <f t="shared" si="0"/>
+        <v>0.29951877209407002</v>
+      </c>
+      <c r="O14">
+        <f t="shared" si="0"/>
+        <v>0.291025929612439</v>
+      </c>
+      <c r="P14">
+        <f t="shared" si="0"/>
+        <v>0.31296740220024999</v>
+      </c>
+      <c r="Q14">
+        <f t="shared" si="0"/>
+        <v>0.28825549023491398</v>
+      </c>
+      <c r="R14">
+        <f>MAX(G14:Q14)</f>
+        <v>0.33537643784593801</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{274BC4E3-A8C9-BE45-8913-D2C1BDCA45EB}">
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="3" max="3" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1" s="20"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2" s="20"/>
+      <c r="B2" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3" s="20"/>
+      <c r="B3" s="20"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="20"/>
+      <c r="F3" s="20"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4" s="20"/>
+      <c r="B4" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" s="22" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="F4" s="20"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5" s="20"/>
+      <c r="B5" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="23">
+        <v>0.84556829268292599</v>
+      </c>
+      <c r="D5" s="23">
+        <v>0.853794298207594</v>
+      </c>
+      <c r="E5" s="23">
+        <f>D5-C5</f>
+        <v>8.2260055246680119E-3</v>
+      </c>
+      <c r="F5" s="20"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6" s="20"/>
+      <c r="B6" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" s="23">
+        <v>0.749</v>
+      </c>
+      <c r="D6" s="23">
+        <v>0.75792075706620698</v>
+      </c>
+      <c r="E6" s="23">
+        <f t="shared" ref="E6:E9" si="0">D6-C6</f>
+        <v>8.9207570662069857E-3</v>
+      </c>
+      <c r="F6" s="20"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7" s="20"/>
+      <c r="B7" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="23">
+        <v>0.31522345679012298</v>
+      </c>
+      <c r="D7" s="23">
+        <v>0.33537643784593801</v>
+      </c>
+      <c r="E7" s="23">
+        <f t="shared" si="0"/>
+        <v>2.0152981055815034E-2</v>
+      </c>
+      <c r="F7" s="20"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8" s="20"/>
+      <c r="B8" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="23">
+        <v>0.34599999999999997</v>
+      </c>
+      <c r="D8" s="23">
+        <v>0.36366962680555998</v>
+      </c>
+      <c r="E8" s="23">
+        <f t="shared" si="0"/>
+        <v>1.7669626805560001E-2</v>
+      </c>
+      <c r="F8" s="20"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A9" s="20"/>
+      <c r="B9" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" s="25">
+        <f>AVERAGE(C5:C8)</f>
+        <v>0.56394793736826232</v>
+      </c>
+      <c r="D9" s="25">
+        <f>AVERAGE(D5:D8)</f>
+        <v>0.57769027998132472</v>
+      </c>
+      <c r="E9" s="25">
+        <f t="shared" si="0"/>
+        <v>1.3742342613062397E-2</v>
+      </c>
+      <c r="F9" s="20"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A10" s="20"/>
+      <c r="B10" s="20"/>
+      <c r="C10" s="20"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="20"/>
+      <c r="F10" s="20"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11" s="20"/>
+      <c r="B11" s="20"/>
+      <c r="C11" s="20"/>
+      <c r="D11" s="20"/>
+      <c r="E11" s="20"/>
+      <c r="F11" s="20"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97944F8B-5231-6846-A13D-49CBD08223D8}">
+  <dimension ref="A1:I11"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="3" max="3" width="21" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="23.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1" s="20"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A2" s="20"/>
+      <c r="B2" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2" s="21"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A3" s="20"/>
+      <c r="B3" s="20"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="20"/>
+      <c r="F3" s="20"/>
+      <c r="G3" s="20"/>
+      <c r="H3" s="20"/>
+      <c r="I3" s="20"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A4" s="20"/>
+      <c r="B4" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="E4" s="22" t="s">
+        <v>32</v>
+      </c>
+      <c r="F4" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="G4" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="H4" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="I4" s="20"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A5" s="20"/>
+      <c r="B5" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="23">
+        <v>0.84146341463414598</v>
+      </c>
+      <c r="D5" s="23">
+        <v>0.84556829268292599</v>
+      </c>
+      <c r="E5" s="23">
+        <v>0.853794298207594</v>
+      </c>
+      <c r="F5" s="23">
+        <f>D5-C5</f>
+        <v>4.1048780487800141E-3</v>
+      </c>
+      <c r="G5" s="23">
+        <f>E5-C5</f>
+        <v>1.2330883573448026E-2</v>
+      </c>
+      <c r="H5" s="23">
+        <f>E5-D5</f>
+        <v>8.2260055246680119E-3</v>
+      </c>
+      <c r="I5" s="20"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A6" s="20"/>
+      <c r="B6" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" s="23">
+        <v>0.74</v>
+      </c>
+      <c r="D6" s="23">
+        <v>0.749</v>
+      </c>
+      <c r="E6" s="23">
+        <v>0.75792075706620698</v>
+      </c>
+      <c r="F6" s="23">
+        <f t="shared" ref="F6:F9" si="0">D6-C6</f>
+        <v>9.000000000000008E-3</v>
+      </c>
+      <c r="G6" s="23">
+        <f t="shared" ref="G6:G9" si="1">E6-C6</f>
+        <v>1.7920757066206994E-2</v>
+      </c>
+      <c r="H6" s="23">
+        <f t="shared" ref="H6:H9" si="2">E6-D6</f>
+        <v>8.9207570662069857E-3</v>
+      </c>
+      <c r="I6" s="20"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A7" s="20"/>
+      <c r="B7" s="28" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="29">
+        <v>0.296296296296296</v>
+      </c>
+      <c r="D7" s="29">
+        <v>0.31522345679012298</v>
+      </c>
+      <c r="E7" s="29">
+        <v>0.33537643784593801</v>
+      </c>
+      <c r="F7" s="29">
+        <f t="shared" si="0"/>
+        <v>1.8927160493826978E-2</v>
+      </c>
+      <c r="G7" s="29">
+        <f t="shared" si="1"/>
+        <v>3.9080141549642011E-2</v>
+      </c>
+      <c r="H7" s="29">
+        <f t="shared" si="2"/>
+        <v>2.0152981055815034E-2</v>
+      </c>
+      <c r="I7" s="20"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A8" s="20"/>
+      <c r="B8" s="30" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="31">
+        <v>0.372</v>
+      </c>
+      <c r="D8" s="31">
+        <v>0.34599999999999997</v>
+      </c>
+      <c r="E8" s="31">
+        <v>0.36366962680555998</v>
+      </c>
+      <c r="F8" s="31">
+        <f t="shared" si="0"/>
+        <v>-2.6000000000000023E-2</v>
+      </c>
+      <c r="G8" s="31">
+        <f t="shared" si="1"/>
+        <v>-8.3303731944400217E-3</v>
+      </c>
+      <c r="H8" s="31">
+        <f t="shared" si="2"/>
+        <v>1.7669626805560001E-2</v>
+      </c>
+      <c r="I8" s="20"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A9" s="20"/>
+      <c r="B9" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" s="27">
+        <f>AVERAGE(C5:C8)</f>
+        <v>0.56243992773261053</v>
+      </c>
+      <c r="D9" s="27">
+        <f>AVERAGE(D5:D8)</f>
+        <v>0.56394793736826232</v>
+      </c>
+      <c r="E9" s="27">
+        <f>AVERAGE(E5:E8)</f>
+        <v>0.57769027998132472</v>
+      </c>
+      <c r="F9" s="32">
+        <f t="shared" si="0"/>
+        <v>1.5080096356517858E-3</v>
+      </c>
+      <c r="G9" s="32">
+        <f t="shared" si="1"/>
+        <v>1.5250352248714183E-2</v>
+      </c>
+      <c r="H9" s="27">
+        <f t="shared" si="2"/>
+        <v>1.3742342613062397E-2</v>
+      </c>
+      <c r="I9" s="20"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A10" s="20"/>
+      <c r="B10" s="20"/>
+      <c r="C10" s="20"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="20"/>
+      <c r="F10" s="20"/>
+      <c r="G10" s="20"/>
+      <c r="H10" s="20"/>
+      <c r="I10" s="20"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A11" s="20"/>
+      <c r="B11" s="20"/>
+      <c r="C11" s="20"/>
+      <c r="D11" s="20"/>
+      <c r="E11" s="20"/>
+      <c r="F11" s="20"/>
+      <c r="G11" s="20"/>
+      <c r="H11" s="20"/>
+      <c r="I11" s="20"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>